--- a/Excel/LegacyGradeConfig.xlsx
+++ b/Excel/LegacyGradeConfig.xlsx
@@ -1304,7 +1304,7 @@
         <v>10000</v>
       </c>
       <c r="N6" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1342,7 +1342,7 @@
         <v>10000</v>
       </c>
       <c r="N7" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1380,7 +1380,7 @@
         <v>10000</v>
       </c>
       <c r="N8" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1418,7 +1418,7 @@
         <v>10000</v>
       </c>
       <c r="N9" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1456,7 +1456,7 @@
         <v>10000</v>
       </c>
       <c r="N10" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1494,7 +1494,7 @@
         <v>10000</v>
       </c>
       <c r="N11" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1532,7 +1532,7 @@
         <v>10000</v>
       </c>
       <c r="N12" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1570,7 +1570,7 @@
         <v>10000</v>
       </c>
       <c r="N13" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
@@ -1609,7 +1609,7 @@
         <v>10000</v>
       </c>
       <c r="N15" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1647,7 +1647,7 @@
         <v>10000</v>
       </c>
       <c r="N16" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O16" s="4"/>
     </row>
@@ -1686,7 +1686,7 @@
         <v>10000</v>
       </c>
       <c r="N17" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O17" s="4"/>
     </row>
@@ -1725,7 +1725,7 @@
         <v>10000</v>
       </c>
       <c r="N18" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O18" s="4"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>10000</v>
       </c>
       <c r="N19" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O19" s="4"/>
     </row>
@@ -1803,7 +1803,7 @@
         <v>10000</v>
       </c>
       <c r="N20" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O20" s="4"/>
     </row>
@@ -1842,7 +1842,7 @@
         <v>10000</v>
       </c>
       <c r="N21" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O21" s="4"/>
     </row>
@@ -1881,7 +1881,7 @@
         <v>10000</v>
       </c>
       <c r="N22" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O22" s="4"/>
     </row>
@@ -1926,7 +1926,7 @@
         <v>10000</v>
       </c>
       <c r="N24" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O24" s="4"/>
     </row>
@@ -1965,7 +1965,7 @@
         <v>10000</v>
       </c>
       <c r="N25" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O25" s="4"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>10000</v>
       </c>
       <c r="N26" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O26" s="4"/>
     </row>
@@ -2043,7 +2043,7 @@
         <v>10000</v>
       </c>
       <c r="N27" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O27" s="4"/>
     </row>
@@ -2082,7 +2082,7 @@
         <v>10000</v>
       </c>
       <c r="N28" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O28" s="4"/>
     </row>
@@ -2121,7 +2121,7 @@
         <v>10000</v>
       </c>
       <c r="N29" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O29" s="4"/>
     </row>
@@ -2160,7 +2160,7 @@
         <v>10000</v>
       </c>
       <c r="N30" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O30" s="4"/>
     </row>
@@ -2199,7 +2199,7 @@
         <v>10000</v>
       </c>
       <c r="N31" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O31" s="4"/>
     </row>

--- a/Excel/LegacyGradeConfig.xlsx
+++ b/Excel/LegacyGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="50">
   <si>
     <t>#</t>
   </si>
@@ -80,58 +80,103 @@
     <t>long</t>
   </si>
   <si>
-    <t>3,1004,2004</t>
-  </si>
-  <si>
-    <t>200,5,1</t>
+    <t>4,3,1003,2003</t>
+  </si>
+  <si>
+    <t>200,200,5,1</t>
   </si>
   <si>
     <t>0,0,10,20</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>2,1004,2004</t>
-  </si>
-  <si>
-    <t>100,2,1</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>1,1004,2004</t>
-  </si>
-  <si>
-    <t>2000,2,1</t>
-  </si>
-  <si>
-    <t>3,1005,2005</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>4,2,1002,2002</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>2,1005,2005</t>
-  </si>
-  <si>
-    <t>1,1005,2005</t>
-  </si>
-  <si>
-    <t>3,1006,2005</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>2,1006,2005</t>
-  </si>
-  <si>
-    <t>1,1006,2005</t>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>100,100,2,1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>4,1,1001,2001</t>
+  </si>
+  <si>
+    <t>100,1000,2,1</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
+    <t>5,3,1003,2003</t>
+  </si>
+  <si>
+    <t>5,2,1002,2002</t>
+  </si>
+  <si>
+    <t>5,1,1001,2001</t>
+  </si>
+  <si>
+    <t>6,3,1003,2003</t>
+  </si>
+  <si>
+    <t>6,2,1002,2002</t>
+  </si>
+  <si>
+    <t>6,1,1001,2001</t>
   </si>
 </sst>
 </file>
@@ -769,7 +814,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -777,6 +821,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1110,8 +1155,7 @@
     <col min="10" max="10" width="12.9166666666667" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.25" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="11.75" style="3" customWidth="1"/>
-    <col min="15" max="15" width="10.5" style="4" customWidth="1"/>
+    <col min="13" max="15" width="11.75" style="3" customWidth="1"/>
     <col min="16" max="16364" width="9" style="2"/>
     <col min="16365" max="16384" width="9" style="1"/>
   </cols>
@@ -1127,7 +1171,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1142,132 +1186,132 @@
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="L3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="6"/>
+      <c r="O3" s="5"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="L4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="6"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="6"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C6" s="1">
@@ -1276,10 +1320,10 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="7">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>10</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -1297,14 +1341,17 @@
       <c r="K6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="1">
-        <v>10</v>
+      <c r="L6" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M6" s="1">
         <v>10000</v>
       </c>
       <c r="N6" s="1">
         <v>10</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1314,14 +1361,14 @@
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
         <v>10</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>18</v>
@@ -1330,19 +1377,22 @@
         <v>19</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="1">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M7" s="1">
         <v>10000</v>
       </c>
       <c r="N7" s="1">
         <v>10</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1352,35 +1402,38 @@
       <c r="D8" s="1">
         <v>3</v>
       </c>
-      <c r="E8" s="7">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
         <v>10</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="1">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M8" s="1">
         <v>10000</v>
       </c>
       <c r="N8" s="1">
         <v>10</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1390,35 +1443,38 @@
       <c r="D9" s="1">
         <v>4</v>
       </c>
-      <c r="E9" s="7">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
         <v>10</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="1">
-        <v>10</v>
+      <c r="L9" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M9" s="1">
         <v>10000</v>
       </c>
       <c r="N9" s="1">
         <v>10</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1428,35 +1484,38 @@
       <c r="D10" s="1">
         <v>5</v>
       </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6">
         <v>10</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="1">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M10" s="1">
         <v>10000</v>
       </c>
       <c r="N10" s="1">
         <v>10</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1466,35 +1525,38 @@
       <c r="D11" s="1">
         <v>6</v>
       </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6">
         <v>10</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="1">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M11" s="1">
         <v>10000</v>
       </c>
       <c r="N11" s="1">
         <v>10</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1504,35 +1566,38 @@
       <c r="D12" s="1">
         <v>7</v>
       </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
         <v>10</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="1">
-        <v>10</v>
+        <v>40</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M12" s="1">
         <v>10000</v>
       </c>
       <c r="N12" s="1">
         <v>10</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1542,29 +1607,29 @@
       <c r="D13" s="1">
         <v>8</v>
       </c>
-      <c r="E13" s="7">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="6">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
         <v>10</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="1">
-        <v>10</v>
+      <c r="L13" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M13" s="1">
         <v>10000</v>
@@ -1572,8 +1637,13 @@
       <c r="N13" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1"/>
+      <c r="O13" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O14" s="7"/>
+    </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C15" s="1">
         <v>9</v>
@@ -1581,14 +1651,14 @@
       <c r="D15" s="1">
         <v>9</v>
       </c>
-      <c r="E15" s="7">
-        <v>1</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6">
         <v>10</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>18</v>
@@ -1597,13 +1667,13 @@
         <v>19</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="1">
-        <v>10</v>
+      <c r="L15" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M15" s="1">
         <v>10000</v>
@@ -1611,6 +1681,9 @@
       <c r="N15" s="1">
         <v>10</v>
       </c>
+      <c r="O15" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C16" s="1">
@@ -1619,14 +1692,14 @@
       <c r="D16" s="1">
         <v>10</v>
       </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E16" s="6">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6">
         <v>10</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>18</v>
@@ -1635,13 +1708,13 @@
         <v>19</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="1">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M16" s="1">
         <v>10000</v>
@@ -1649,7 +1722,9 @@
       <c r="N16" s="1">
         <v>10</v>
       </c>
-      <c r="O16" s="4"/>
+      <c r="O16" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C17" s="1">
@@ -1658,29 +1733,29 @@
       <c r="D17" s="1">
         <v>11</v>
       </c>
-      <c r="E17" s="7">
-        <v>1</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E17" s="6">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6">
         <v>10</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" s="1">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M17" s="1">
         <v>10000</v>
@@ -1688,7 +1763,9 @@
       <c r="N17" s="1">
         <v>10</v>
       </c>
-      <c r="O17" s="4"/>
+      <c r="O17" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C18" s="1">
@@ -1697,29 +1774,29 @@
       <c r="D18" s="1">
         <v>12</v>
       </c>
-      <c r="E18" s="7">
-        <v>1</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E18" s="6">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6">
         <v>10</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="1">
-        <v>10</v>
+      <c r="L18" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M18" s="1">
         <v>10000</v>
@@ -1727,7 +1804,9 @@
       <c r="N18" s="1">
         <v>10</v>
       </c>
-      <c r="O18" s="4"/>
+      <c r="O18" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C19" s="1">
@@ -1736,29 +1815,29 @@
       <c r="D19" s="1">
         <v>13</v>
       </c>
-      <c r="E19" s="7">
-        <v>1</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="E19" s="6">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6">
         <v>10</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L19" s="1">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M19" s="1">
         <v>10000</v>
@@ -1766,7 +1845,9 @@
       <c r="N19" s="1">
         <v>10</v>
       </c>
-      <c r="O19" s="4"/>
+      <c r="O19" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C20" s="1">
@@ -1775,29 +1856,29 @@
       <c r="D20" s="1">
         <v>14</v>
       </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="7">
+      <c r="E20" s="6">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6">
         <v>10</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L20" s="1">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M20" s="1">
         <v>10000</v>
@@ -1805,7 +1886,9 @@
       <c r="N20" s="1">
         <v>10</v>
       </c>
-      <c r="O20" s="4"/>
+      <c r="O20" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C21" s="1">
@@ -1814,29 +1897,29 @@
       <c r="D21" s="1">
         <v>15</v>
       </c>
-      <c r="E21" s="7">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7">
+      <c r="E21" s="6">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6">
         <v>10</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" s="1">
-        <v>10</v>
+        <v>40</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M21" s="1">
         <v>10000</v>
@@ -1844,7 +1927,9 @@
       <c r="N21" s="1">
         <v>10</v>
       </c>
-      <c r="O21" s="4"/>
+      <c r="O21" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C22" s="1">
@@ -1853,29 +1938,29 @@
       <c r="D22" s="1">
         <v>16</v>
       </c>
-      <c r="E22" s="7">
-        <v>1</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E22" s="6">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6">
         <v>10</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" s="1">
-        <v>10</v>
+      <c r="L22" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M22" s="1">
         <v>10000</v>
@@ -1883,13 +1968,15 @@
       <c r="N22" s="1">
         <v>10</v>
       </c>
-      <c r="O22" s="4"/>
+      <c r="O22" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="I23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
+      <c r="O23" s="3"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="1">
@@ -1898,14 +1985,14 @@
       <c r="D24" s="1">
         <v>17</v>
       </c>
-      <c r="E24" s="7">
-        <v>1</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E24" s="6">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6">
         <v>10</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>18</v>
@@ -1914,13 +2001,13 @@
         <v>19</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L24" s="1">
-        <v>10</v>
+      <c r="L24" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M24" s="1">
         <v>10000</v>
@@ -1928,7 +2015,9 @@
       <c r="N24" s="1">
         <v>10</v>
       </c>
-      <c r="O24" s="4"/>
+      <c r="O24" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="1">
@@ -1937,14 +2026,14 @@
       <c r="D25" s="1">
         <v>18</v>
       </c>
-      <c r="E25" s="7">
-        <v>1</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="6">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6">
         <v>10</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>18</v>
@@ -1953,13 +2042,13 @@
         <v>19</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" s="1">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M25" s="1">
         <v>10000</v>
@@ -1967,7 +2056,9 @@
       <c r="N25" s="1">
         <v>10</v>
       </c>
-      <c r="O25" s="4"/>
+      <c r="O25" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="1">
@@ -1976,29 +2067,29 @@
       <c r="D26" s="1">
         <v>19</v>
       </c>
-      <c r="E26" s="7">
-        <v>1</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E26" s="6">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6">
         <v>10</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" s="1">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M26" s="1">
         <v>10000</v>
@@ -2006,7 +2097,9 @@
       <c r="N26" s="1">
         <v>10</v>
       </c>
-      <c r="O26" s="4"/>
+      <c r="O26" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="1">
@@ -2015,29 +2108,29 @@
       <c r="D27" s="1">
         <v>20</v>
       </c>
-      <c r="E27" s="7">
-        <v>1</v>
-      </c>
-      <c r="F27" s="7">
+      <c r="E27" s="6">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6">
         <v>10</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H27" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" s="1">
-        <v>10</v>
+      <c r="L27" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M27" s="1">
         <v>10000</v>
@@ -2045,7 +2138,9 @@
       <c r="N27" s="1">
         <v>10</v>
       </c>
-      <c r="O27" s="4"/>
+      <c r="O27" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="1">
@@ -2054,29 +2149,29 @@
       <c r="D28" s="1">
         <v>21</v>
       </c>
-      <c r="E28" s="7">
-        <v>1</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6">
         <v>10</v>
       </c>
       <c r="G28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="I28" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L28" s="1">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M28" s="1">
         <v>10000</v>
@@ -2084,7 +2179,9 @@
       <c r="N28" s="1">
         <v>10</v>
       </c>
-      <c r="O28" s="4"/>
+      <c r="O28" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="1">
@@ -2093,29 +2190,29 @@
       <c r="D29" s="1">
         <v>22</v>
       </c>
-      <c r="E29" s="7">
-        <v>1</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E29" s="6">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6">
         <v>10</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="1">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M29" s="1">
         <v>10000</v>
@@ -2123,7 +2220,9 @@
       <c r="N29" s="1">
         <v>10</v>
       </c>
-      <c r="O29" s="4"/>
+      <c r="O29" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C30" s="1">
@@ -2132,29 +2231,29 @@
       <c r="D30" s="1">
         <v>23</v>
       </c>
-      <c r="E30" s="7">
-        <v>1</v>
-      </c>
-      <c r="F30" s="7">
+      <c r="E30" s="6">
+        <v>1</v>
+      </c>
+      <c r="F30" s="6">
         <v>10</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L30" s="1">
-        <v>10</v>
+        <v>40</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M30" s="1">
         <v>10000</v>
@@ -2162,7 +2261,9 @@
       <c r="N30" s="1">
         <v>10</v>
       </c>
-      <c r="O30" s="4"/>
+      <c r="O30" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C31" s="1">
@@ -2171,29 +2272,29 @@
       <c r="D31" s="1">
         <v>24</v>
       </c>
-      <c r="E31" s="7">
-        <v>1</v>
-      </c>
-      <c r="F31" s="7">
+      <c r="E31" s="6">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6">
         <v>10</v>
       </c>
       <c r="G31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="I31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K31" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L31" s="1">
-        <v>10</v>
+      <c r="L31" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M31" s="1">
         <v>10000</v>
@@ -2201,13 +2302,15 @@
       <c r="N31" s="1">
         <v>10</v>
       </c>
-      <c r="O31" s="4"/>
+      <c r="O31" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="I32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
-      <c r="O32" s="4"/>
+      <c r="O32" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/LegacyGradeConfig.xlsx
+++ b/Excel/LegacyGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>30</t>
+  </si>
+  <si>
+    <t>100000</t>
   </si>
   <si>
     <t>攻速</t>
@@ -809,7 +812,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -821,8 +824,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1142,7 +1146,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1324,15 +1328,15 @@
         <v>1</v>
       </c>
       <c r="F6" s="6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J6" s="8" t="s">
@@ -1344,14 +1348,14 @@
       <c r="L6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="1">
-        <v>10000</v>
+      <c r="M6" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N6" s="1">
         <v>10</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1365,34 +1369,34 @@
         <v>1</v>
       </c>
       <c r="F7" s="6">
-        <v>10</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="1">
-        <v>10000</v>
+      <c r="M7" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N7" s="1">
         <v>10</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1406,19 +1410,19 @@
         <v>1</v>
       </c>
       <c r="F8" s="6">
-        <v>10</v>
-      </c>
-      <c r="G8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="H8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>21</v>
@@ -1426,14 +1430,14 @@
       <c r="L8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="1">
-        <v>10000</v>
+      <c r="M8" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N8" s="1">
         <v>10</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1447,34 +1451,34 @@
         <v>1</v>
       </c>
       <c r="F9" s="6">
-        <v>10</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="1">
-        <v>10000</v>
+      <c r="M9" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N9" s="1">
         <v>10</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1488,34 +1492,34 @@
         <v>1</v>
       </c>
       <c r="F10" s="6">
-        <v>10</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="H10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="1">
-        <v>10000</v>
+      <c r="M10" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N10" s="1">
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1529,34 +1533,34 @@
         <v>1</v>
       </c>
       <c r="F11" s="6">
-        <v>10</v>
-      </c>
-      <c r="G11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="H11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="1">
-        <v>10000</v>
+      <c r="M11" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N11" s="1">
         <v>10</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1570,34 +1574,34 @@
         <v>1</v>
       </c>
       <c r="F12" s="6">
-        <v>10</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="H12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="1">
-        <v>10000</v>
+      <c r="M12" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N12" s="1">
         <v>10</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1611,38 +1615,41 @@
         <v>1</v>
       </c>
       <c r="F13" s="6">
-        <v>10</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="H13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M13" s="1">
-        <v>10000</v>
+      <c r="M13" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N13" s="1">
         <v>10</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O14" s="7"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="3"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C15" s="1">
@@ -1655,15 +1662,15 @@
         <v>1</v>
       </c>
       <c r="F15" s="6">
-        <v>10</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J15" s="8" t="s">
@@ -1675,14 +1682,14 @@
       <c r="L15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="1">
-        <v>10000</v>
+      <c r="M15" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N15" s="1">
         <v>10</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -1696,34 +1703,34 @@
         <v>1</v>
       </c>
       <c r="F16" s="6">
-        <v>10</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="1">
-        <v>10000</v>
+      <c r="M16" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N16" s="1">
         <v>10</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1737,19 +1744,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="6">
-        <v>10</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>21</v>
@@ -1757,14 +1764,14 @@
       <c r="L17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M17" s="1">
-        <v>10000</v>
+      <c r="M17" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N17" s="1">
         <v>10</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1778,34 +1785,34 @@
         <v>1</v>
       </c>
       <c r="F18" s="6">
-        <v>10</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="1">
-        <v>10000</v>
+      <c r="M18" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N18" s="1">
         <v>10</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1819,34 +1826,34 @@
         <v>1</v>
       </c>
       <c r="F19" s="6">
-        <v>10</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M19" s="1">
-        <v>10000</v>
+      <c r="M19" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N19" s="1">
         <v>10</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1860,34 +1867,34 @@
         <v>1</v>
       </c>
       <c r="F20" s="6">
-        <v>10</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="1">
-        <v>10000</v>
+      <c r="M20" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N20" s="1">
         <v>10</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1901,34 +1908,34 @@
         <v>1</v>
       </c>
       <c r="F21" s="6">
-        <v>10</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="1">
-        <v>10000</v>
+      <c r="M21" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N21" s="1">
         <v>10</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1942,38 +1949,41 @@
         <v>1</v>
       </c>
       <c r="F22" s="6">
-        <v>10</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M22" s="1">
-        <v>10000</v>
+      <c r="M22" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N22" s="1">
         <v>10</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="I23" s="3"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1989,15 +1999,15 @@
         <v>1</v>
       </c>
       <c r="F24" s="6">
-        <v>10</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J24" s="8" t="s">
@@ -2009,14 +2019,14 @@
       <c r="L24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M24" s="1">
-        <v>10000</v>
+      <c r="M24" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N24" s="1">
         <v>10</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2030,34 +2040,34 @@
         <v>1</v>
       </c>
       <c r="F25" s="6">
-        <v>10</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M25" s="1">
-        <v>10000</v>
+      <c r="M25" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N25" s="1">
         <v>10</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2071,19 +2081,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="6">
-        <v>10</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>21</v>
@@ -2091,14 +2101,14 @@
       <c r="L26" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M26" s="1">
-        <v>10000</v>
+      <c r="M26" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N26" s="1">
         <v>10</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2112,34 +2122,34 @@
         <v>1</v>
       </c>
       <c r="F27" s="6">
-        <v>10</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M27" s="1">
-        <v>10000</v>
+      <c r="M27" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N27" s="1">
         <v>10</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2153,34 +2163,34 @@
         <v>1</v>
       </c>
       <c r="F28" s="6">
-        <v>10</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M28" s="1">
-        <v>10000</v>
+      <c r="M28" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N28" s="1">
         <v>10</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2194,34 +2204,34 @@
         <v>1</v>
       </c>
       <c r="F29" s="6">
-        <v>10</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M29" s="1">
-        <v>10000</v>
+      <c r="M29" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N29" s="1">
         <v>10</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2235,34 +2245,34 @@
         <v>1</v>
       </c>
       <c r="F30" s="6">
-        <v>10</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M30" s="1">
-        <v>10000</v>
+      <c r="M30" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N30" s="1">
         <v>10</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2276,41 +2286,1188 @@
         <v>1</v>
       </c>
       <c r="F31" s="6">
-        <v>10</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M31" s="1">
-        <v>10000</v>
+      <c r="M31" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="N31" s="1">
         <v>10</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="I32" s="3"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:15">
+      <c r="A33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1">
+        <v>25</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N33" s="3">
+        <v>10</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:15">
+      <c r="A34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="1">
+        <v>26</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
+        <v>10</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N34" s="3">
+        <v>10</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:15">
+      <c r="A35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="1">
+        <v>27</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>10</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N35" s="3">
+        <v>10</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:15">
+      <c r="A36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1">
+        <v>28</v>
+      </c>
+      <c r="D36" s="1">
+        <v>4</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N36" s="3">
+        <v>10</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:15">
+      <c r="A37" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1">
+        <v>29</v>
+      </c>
+      <c r="D37" s="1">
+        <v>5</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>10</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N37" s="3">
+        <v>10</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:15">
+      <c r="A38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="1">
+        <v>30</v>
+      </c>
+      <c r="D38" s="1">
+        <v>6</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>10</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N38" s="3">
+        <v>10</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:15">
+      <c r="A39" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>31</v>
+      </c>
+      <c r="D39" s="1">
+        <v>7</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>10</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N39" s="3">
+        <v>10</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:15">
+      <c r="A40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>32</v>
+      </c>
+      <c r="D40" s="1">
+        <v>8</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>10</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N40" s="3">
+        <v>10</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:15">
+      <c r="A41" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:15">
+      <c r="A42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>33</v>
+      </c>
+      <c r="D42" s="1">
+        <v>9</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>10</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N42" s="3">
+        <v>10</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:15">
+      <c r="A43" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1">
+        <v>34</v>
+      </c>
+      <c r="D43" s="1">
+        <v>10</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>10</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N43" s="3">
+        <v>10</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:15">
+      <c r="A44" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>35</v>
+      </c>
+      <c r="D44" s="1">
+        <v>11</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>10</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N44" s="3">
+        <v>10</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:15">
+      <c r="A45" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1">
+        <v>36</v>
+      </c>
+      <c r="D45" s="1">
+        <v>12</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>10</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N45" s="3">
+        <v>10</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:15">
+      <c r="A46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1">
+        <v>37</v>
+      </c>
+      <c r="D46" s="1">
+        <v>13</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
+        <v>10</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N46" s="3">
+        <v>10</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:15">
+      <c r="A47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1">
+        <v>38</v>
+      </c>
+      <c r="D47" s="1">
+        <v>14</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>10</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N47" s="3">
+        <v>10</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:15">
+      <c r="A48" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1">
+        <v>39</v>
+      </c>
+      <c r="D48" s="1">
+        <v>15</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>10</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N48" s="3">
+        <v>10</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:15">
+      <c r="A49" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="1">
+        <v>40</v>
+      </c>
+      <c r="D49" s="1">
+        <v>16</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
+        <v>10</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N49" s="3">
+        <v>10</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:15">
+      <c r="A50" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:15">
+      <c r="A51" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1">
+        <v>41</v>
+      </c>
+      <c r="D51" s="1">
+        <v>17</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1">
+        <v>10</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M51" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N51" s="3">
+        <v>10</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:15">
+      <c r="A52" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1">
+        <v>42</v>
+      </c>
+      <c r="D52" s="1">
+        <v>18</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
+        <v>10</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M52" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N52" s="3">
+        <v>10</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:15">
+      <c r="A53" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1">
+        <v>43</v>
+      </c>
+      <c r="D53" s="1">
+        <v>19</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1">
+        <v>10</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M53" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N53" s="3">
+        <v>10</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:15">
+      <c r="A54" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="1">
+        <v>44</v>
+      </c>
+      <c r="D54" s="1">
+        <v>20</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1">
+        <v>10</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M54" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N54" s="3">
+        <v>10</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:15">
+      <c r="A55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="1">
+        <v>45</v>
+      </c>
+      <c r="D55" s="1">
+        <v>21</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1">
+        <v>10</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M55" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N55" s="3">
+        <v>10</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:15">
+      <c r="A56" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="1">
+        <v>46</v>
+      </c>
+      <c r="D56" s="1">
+        <v>22</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1">
+        <v>10</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N56" s="3">
+        <v>10</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:15">
+      <c r="A57" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1">
+        <v>47</v>
+      </c>
+      <c r="D57" s="1">
+        <v>23</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
+        <v>10</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M57" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N57" s="3">
+        <v>10</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:15">
+      <c r="A58" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="1">
+        <v>48</v>
+      </c>
+      <c r="D58" s="1">
+        <v>24</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1">
+        <v>10</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N58" s="3">
+        <v>10</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/LegacyGradeConfig.xlsx
+++ b/Excel/LegacyGradeConfig.xlsx
@@ -1352,7 +1352,7 @@
         <v>23</v>
       </c>
       <c r="N6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>24</v>
@@ -1393,7 +1393,7 @@
         <v>23</v>
       </c>
       <c r="N7" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>28</v>
@@ -1686,7 +1686,7 @@
         <v>23</v>
       </c>
       <c r="N15" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>24</v>
@@ -1727,7 +1727,7 @@
         <v>23</v>
       </c>
       <c r="N16" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>28</v>
@@ -2023,7 +2023,7 @@
         <v>23</v>
       </c>
       <c r="N24" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>24</v>
@@ -2064,7 +2064,7 @@
         <v>23</v>
       </c>
       <c r="N25" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>28</v>

--- a/Excel/LegacyGradeConfig.xlsx
+++ b/Excel/LegacyGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="53">
   <si>
     <t>#</t>
   </si>
@@ -83,103 +83,109 @@
     <t>4,3,1003,2003</t>
   </si>
   <si>
+    <t>200,200,2,1</t>
+  </si>
+  <si>
+    <t>0,0,10,20</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>4,2,1002,2002</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>100,100,1,1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>4,1,1001,2001</t>
+  </si>
+  <si>
+    <t>100,1000,2,1</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
+    <t>5,3,1003,2003</t>
+  </si>
+  <si>
+    <t>5,2,1002,2002</t>
+  </si>
+  <si>
+    <t>5,1,1001,2001</t>
+  </si>
+  <si>
+    <t>6,3,1003,2003</t>
+  </si>
+  <si>
+    <t>6,2,1002,2002</t>
+  </si>
+  <si>
+    <t>6,1,1001,2001</t>
+  </si>
+  <si>
     <t>200,200,5,1</t>
   </si>
   <si>
-    <t>0,0,10,20</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>攻速</t>
-  </si>
-  <si>
-    <t>4,2,1002,2002</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
     <t>100,100,2,1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>4,1,1001,2001</t>
-  </si>
-  <si>
-    <t>100,1000,2,1</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>增伤</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>移速</t>
-  </si>
-  <si>
-    <t>5,3,1003,2003</t>
-  </si>
-  <si>
-    <t>5,2,1002,2002</t>
-  </si>
-  <si>
-    <t>5,1,1001,2001</t>
-  </si>
-  <si>
-    <t>6,3,1003,2003</t>
-  </si>
-  <si>
-    <t>6,2,1002,2002</t>
-  </si>
-  <si>
-    <t>6,1,1001,2001</t>
   </si>
 </sst>
 </file>
@@ -2348,7 +2354,7 @@
         <v>17</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>19</v>
@@ -2395,7 +2401,7 @@
         <v>25</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>19</v>
@@ -2442,7 +2448,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>19</v>
@@ -2489,7 +2495,7 @@
         <v>25</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>19</v>
@@ -2583,7 +2589,7 @@
         <v>17</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>19</v>
@@ -2732,7 +2738,7 @@
         <v>45</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>19</v>
@@ -2779,7 +2785,7 @@
         <v>46</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>19</v>
@@ -2826,7 +2832,7 @@
         <v>45</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>19</v>
@@ -2873,7 +2879,7 @@
         <v>46</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>19</v>
@@ -2967,7 +2973,7 @@
         <v>45</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>19</v>
@@ -3116,7 +3122,7 @@
         <v>48</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I51" s="9" t="s">
         <v>19</v>
@@ -3163,7 +3169,7 @@
         <v>49</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>19</v>
@@ -3210,7 +3216,7 @@
         <v>48</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>19</v>
@@ -3257,7 +3263,7 @@
         <v>49</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>19</v>
@@ -3351,7 +3357,7 @@
         <v>48</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>19</v>

--- a/Excel/LegacyGradeConfig.xlsx
+++ b/Excel/LegacyGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -80,112 +80,121 @@
     <t>long</t>
   </si>
   <si>
+    <t>4,3,1004,2004</t>
+  </si>
+  <si>
+    <t>200,200,2,1</t>
+  </si>
+  <si>
+    <t>0,0,10,20</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>4,2,1002,2002</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>100,100,1,1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>4,1,1001,2001</t>
+  </si>
+  <si>
+    <t>100,1000,2,1</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
+    <t>5,3,1005,2005</t>
+  </si>
+  <si>
+    <t>5,2,1002,2002</t>
+  </si>
+  <si>
+    <t>5,1,1001,2001</t>
+  </si>
+  <si>
+    <t>6,3,1006,2006</t>
+  </si>
+  <si>
+    <t>6,2,1002,2002</t>
+  </si>
+  <si>
+    <t>6,1,1001,2001</t>
+  </si>
+  <si>
     <t>4,3,1003,2003</t>
   </si>
   <si>
-    <t>200,200,2,1</t>
-  </si>
-  <si>
-    <t>0,0,10,20</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>攻速</t>
-  </si>
-  <si>
-    <t>4,2,1002,2002</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>100,100,1,1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>4,1,1001,2001</t>
-  </si>
-  <si>
-    <t>100,1000,2,1</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>增伤</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>移速</t>
+    <t>200,200,5,1</t>
+  </si>
+  <si>
+    <t>100,100,2,1</t>
   </si>
   <si>
     <t>5,3,1003,2003</t>
   </si>
   <si>
-    <t>5,2,1002,2002</t>
-  </si>
-  <si>
-    <t>5,1,1001,2001</t>
-  </si>
-  <si>
     <t>6,3,1003,2003</t>
-  </si>
-  <si>
-    <t>6,2,1002,2002</t>
-  </si>
-  <si>
-    <t>6,1,1001,2001</t>
-  </si>
-  <si>
-    <t>200,200,5,1</t>
-  </si>
-  <si>
-    <t>100,100,2,1</t>
   </si>
 </sst>
 </file>
@@ -2351,10 +2360,10 @@
         <v>10</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>19</v>
@@ -2401,7 +2410,7 @@
         <v>25</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>19</v>
@@ -2445,10 +2454,10 @@
         <v>10</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>19</v>
@@ -2495,7 +2504,7 @@
         <v>25</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>19</v>
@@ -2586,10 +2595,10 @@
         <v>10</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>19</v>
@@ -2735,10 +2744,10 @@
         <v>10</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>19</v>
@@ -2785,7 +2794,7 @@
         <v>46</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>19</v>
@@ -2829,10 +2838,10 @@
         <v>10</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>19</v>
@@ -2879,7 +2888,7 @@
         <v>46</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>19</v>
@@ -2970,10 +2979,10 @@
         <v>10</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>19</v>
@@ -3119,10 +3128,10 @@
         <v>10</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I51" s="9" t="s">
         <v>19</v>
@@ -3169,7 +3178,7 @@
         <v>49</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>19</v>
@@ -3213,10 +3222,10 @@
         <v>10</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>19</v>
@@ -3263,7 +3272,7 @@
         <v>49</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>19</v>
@@ -3354,10 +3363,10 @@
         <v>10</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>19</v>
